--- a/resultados/Grade_Horarios_UFSC_20261.xlsx
+++ b/resultados/Grade_Horarios_UFSC_20261.xlsx
@@ -190,8 +190,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Legenda_Fase_1" displayName="Legenda_Fase_1" ref="A19:C26" headerRowCount="1">
-  <autoFilter ref="A19:C26"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Legenda_Fase_1" displayName="Legenda_Fase_1" ref="A19:C28" headerRowCount="1">
+  <autoFilter ref="A19:C28"/>
   <tableColumns count="3">
     <tableColumn id="1" name="Cód. (Turma)"/>
     <tableColumn id="2" name="Nome da Disciplina"/>
@@ -217,8 +217,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Legenda_Fase_2" displayName="Legenda_Fase_2" ref="A19:C29" headerRowCount="1">
-  <autoFilter ref="A19:C29"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Legenda_Fase_2" displayName="Legenda_Fase_2" ref="A19:C32" headerRowCount="1">
+  <autoFilter ref="A19:C32"/>
   <tableColumns count="3">
     <tableColumn id="1" name="Cód. (Turma)"/>
     <tableColumn id="2" name="Nome da Disciplina"/>
@@ -244,8 +244,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Legenda_Fase_3" displayName="Legenda_Fase_3" ref="A19:C31" headerRowCount="1">
-  <autoFilter ref="A19:C31"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Legenda_Fase_3" displayName="Legenda_Fase_3" ref="A19:C35" headerRowCount="1">
+  <autoFilter ref="A19:C35"/>
   <tableColumns count="3">
     <tableColumn id="1" name="Cód. (Turma)"/>
     <tableColumn id="2" name="Nome da Disciplina"/>
@@ -271,8 +271,8 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Legenda_Fase_4" displayName="Legenda_Fase_4" ref="A19:C34" headerRowCount="1">
-  <autoFilter ref="A19:C34"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Legenda_Fase_4" displayName="Legenda_Fase_4" ref="A19:C32" headerRowCount="1">
+  <autoFilter ref="A19:C32"/>
   <tableColumns count="3">
     <tableColumn id="1" name="Cód. (Turma)"/>
     <tableColumn id="2" name="Nome da Disciplina"/>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Optativa</t>
+          <t>2ª Fase</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Optativa</t>
+          <t>Obrigatória</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Optativa</t>
+          <t>1ª Fase</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Optativa</t>
+          <t>Obrigatória</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Optativa</t>
+          <t>3ª Fase</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Optativa</t>
+          <t>Obrigatória</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3333,12 +3333,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Optativa</t>
+          <t>3ª Fase</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Optativa</t>
+          <t>Obrigatória</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Optativa</t>
+          <t>1ª Fase</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Optativa</t>
+          <t>Obrigatória</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3568,12 +3568,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Outros / Eletiva</t>
+          <t>3ª Fase</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Optativa</t>
+          <t>Obrigatória</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3615,12 +3615,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Outros / Eletiva</t>
+          <t>3ª Fase</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Optativa</t>
+          <t>Obrigatória</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>4ª Fase</t>
+          <t>2ª Fase</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>4ª Fase</t>
+          <t>2ª Fase</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3890,13 +3890,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
     <col width="63" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="38" customWidth="1" min="6" max="6"/>
   </cols>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7925 (01342)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7925 (01342)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7943 (01342)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7943 (01342)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -4478,49 +4478,83 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LLV7802 (01342C)</t>
+          <t>CIN7925 (01342)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Leitura e Produção do Texto</t>
+          <t>Introdução a Algoritmos</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Graziela Hahn</t>
+          <t>Flavio Augusto Carraro</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LLV7802 (01342D)</t>
+          <t>CIN7943 (01342)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Leitura e Produção do Texto</t>
+          <t>Experiência do Usuário (UX) User Experience</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Graziela Hahn</t>
+          <t>Márcio Matias</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>LLV7802 (01342C)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Leitura e Produção do Texto</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Graziela Hahn</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>LLV7802 (01342D)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Leitura e Produção do Texto</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Graziela Hahn</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>MTM3110 (01342)</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Cálculo</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Camilo Campana e Camila Aparecida Benedito Rodrigues de Lima</t>
         </is>
@@ -4541,14 +4575,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="37" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -4629,7 +4663,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CIN7202 (02342A)</t>
+          <t>CIN7202 (02342A) / INE5111 (04342A)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -4661,7 +4695,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CIN7202 (02342A)</t>
+          <t>CIN7202 (02342A) / INE5111 (04342A)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4698,7 +4732,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>INE5111 (04342A)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4730,7 +4764,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>INE5111 (04342A)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -4912,7 +4946,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>INE5111 (04342C)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -4927,7 +4961,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7907 (02342) / INE5111 (04342C)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -4944,7 +4978,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>INE5111 (04342C)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -4959,7 +4993,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7907 (02342) / INE5111 (04342C)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -4991,7 +5025,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7907 (02342)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -5023,7 +5057,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7907 (02342)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -5225,6 +5259,57 @@
       <c r="C29" t="inlineStr">
         <is>
           <t>Patricia da Silva Neubert</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CIN7907 (02342)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Lógica Aplicada I</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ricardo Alexandre Reinaldo de Moraes e Flavio Augusto Carraro</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>INE5111 (04342A)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Estatística Aplicada I</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Vera do Carmo Comparsi de Vargas</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>INE5111 (04342C)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Estatística Aplicada I</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Manoella Reis Cardenuto</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5326,7 +5411,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7936 (03342A)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -5341,7 +5426,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>HST7921 (03342A)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -5358,7 +5443,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7936 (03342A)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5373,7 +5458,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>HST7921 (03342A)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -5405,7 +5490,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>HST7921 (03342A)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -5437,7 +5522,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>HST7921 (03342A)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5634,7 +5719,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>HST7921 (03342C)</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5751,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>HST7921 (03342C)</t>
         </is>
       </c>
     </row>
@@ -5688,7 +5773,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7936 (03342C)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -5698,7 +5783,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>HST7921 (03342C)</t>
         </is>
       </c>
     </row>
@@ -5720,7 +5805,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7936 (03342C)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -5730,7 +5815,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>HST7921 (03342C)</t>
         </is>
       </c>
     </row>
@@ -5961,6 +6046,74 @@
       <c r="C31" t="inlineStr">
         <is>
           <t>Rogerio da Silva Nunes</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CIN7936 (03342A)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Proteção de Dados Pessoais</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Marcelo Minghelli</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>CIN7936 (03342C)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Proteção de Dados Pessoais</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Marcelo Minghelli</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>HST7921 (03342A)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>História do Brasil Contemporâneo</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Roselane Neckel</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>HST7921 (03342C)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>História do Brasil Contemporâneo</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Roselane Neckel</t>
         </is>
       </c>
     </row>
@@ -5979,7 +6132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6067,7 +6220,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>INE5111 (04342A)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -6099,7 +6252,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>INE5111 (04342A)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -6136,7 +6289,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>INE5111 (04342A)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -6168,7 +6321,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>INE5111 (04342A)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -6350,7 +6503,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>INE5111 (04342C)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -6365,7 +6518,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>INE5111 (04342C)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -6382,7 +6535,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>INE5111 (04342C)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -6397,7 +6550,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>INE5111 (04342C)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -6714,40 +6867,6 @@
       <c r="C32" t="inlineStr">
         <is>
           <t>Sabrina Borges Ramos de Carvalho</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>INE5111 (04342A)</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Estatística Aplicada I</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Vera do Carmo Comparsi de Vargas</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>INE5111 (04342C)</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Estatística Aplicada I</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Manoella Reis Cardenuto</t>
         </is>
       </c>
     </row>

--- a/resultados/Grade_Horarios_UFSC_20261.xlsx
+++ b/resultados/Grade_Horarios_UFSC_20261.xlsx
@@ -151,12 +151,13 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Legenda_Fase_5" displayName="Legenda_Fase_5" ref="A19:C24" headerRowCount="1">
-  <autoFilter ref="A19:C24"/>
-  <tableColumns count="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Legenda_Fase_5" displayName="Legenda_Fase_5" ref="A19:D24" headerRowCount="1">
+  <autoFilter ref="A19:D24"/>
+  <tableColumns count="4">
     <tableColumn id="1" name="Cód. (Turma)"/>
     <tableColumn id="2" name="Nome da Disciplina"/>
-    <tableColumn id="3" name="Professor"/>
+    <tableColumn id="3" name="Local"/>
+    <tableColumn id="4" name="Professor"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -178,24 +179,26 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Legenda_Fase_6" displayName="Legenda_Fase_6" ref="A19:C23" headerRowCount="1">
-  <autoFilter ref="A19:C23"/>
-  <tableColumns count="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Legenda_Fase_6" displayName="Legenda_Fase_6" ref="A19:D23" headerRowCount="1">
+  <autoFilter ref="A19:D23"/>
+  <tableColumns count="4">
     <tableColumn id="1" name="Cód. (Turma)"/>
     <tableColumn id="2" name="Nome da Disciplina"/>
-    <tableColumn id="3" name="Professor"/>
+    <tableColumn id="3" name="Local"/>
+    <tableColumn id="4" name="Professor"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Legenda_Fase_1" displayName="Legenda_Fase_1" ref="A19:C28" headerRowCount="1">
-  <autoFilter ref="A19:C28"/>
-  <tableColumns count="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Legenda_Fase_1" displayName="Legenda_Fase_1" ref="A19:D28" headerRowCount="1">
+  <autoFilter ref="A19:D28"/>
+  <tableColumns count="4">
     <tableColumn id="1" name="Cód. (Turma)"/>
     <tableColumn id="2" name="Nome da Disciplina"/>
-    <tableColumn id="3" name="Professor"/>
+    <tableColumn id="3" name="Local"/>
+    <tableColumn id="4" name="Professor"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -217,12 +220,13 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Legenda_Fase_2" displayName="Legenda_Fase_2" ref="A19:C32" headerRowCount="1">
-  <autoFilter ref="A19:C32"/>
-  <tableColumns count="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Legenda_Fase_2" displayName="Legenda_Fase_2" ref="A19:D34" headerRowCount="1">
+  <autoFilter ref="A19:D34"/>
+  <tableColumns count="4">
     <tableColumn id="1" name="Cód. (Turma)"/>
     <tableColumn id="2" name="Nome da Disciplina"/>
-    <tableColumn id="3" name="Professor"/>
+    <tableColumn id="3" name="Local"/>
+    <tableColumn id="4" name="Professor"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -244,12 +248,13 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Legenda_Fase_3" displayName="Legenda_Fase_3" ref="A19:C35" headerRowCount="1">
-  <autoFilter ref="A19:C35"/>
-  <tableColumns count="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Legenda_Fase_3" displayName="Legenda_Fase_3" ref="A19:D35" headerRowCount="1">
+  <autoFilter ref="A19:D35"/>
+  <tableColumns count="4">
     <tableColumn id="1" name="Cód. (Turma)"/>
     <tableColumn id="2" name="Nome da Disciplina"/>
-    <tableColumn id="3" name="Professor"/>
+    <tableColumn id="3" name="Local"/>
+    <tableColumn id="4" name="Professor"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -271,12 +276,13 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Legenda_Fase_4" displayName="Legenda_Fase_4" ref="A19:C32" headerRowCount="1">
-  <autoFilter ref="A19:C32"/>
-  <tableColumns count="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Legenda_Fase_4" displayName="Legenda_Fase_4" ref="A19:D30" headerRowCount="1">
+  <autoFilter ref="A19:D30"/>
+  <tableColumns count="4">
     <tableColumn id="1" name="Cód. (Turma)"/>
     <tableColumn id="2" name="Nome da Disciplina"/>
-    <tableColumn id="3" name="Professor"/>
+    <tableColumn id="3" name="Local"/>
+    <tableColumn id="4" name="Professor"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -586,51 +592,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:K70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Semestre</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Código da Disciplina</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Turma</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Nome da Disciplina</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Horas Aula</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Ofertas</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Horário/Local</t>
-        </is>
-      </c>
       <c r="I1" t="inlineStr">
+        <is>
+          <t>Horário</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>Professor</t>
         </is>
@@ -639,45 +655,55 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>CIN7141</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>01342C</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Lógica Instrumental I</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>1ª Fase</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>5.2020-2 / CCE-CCE129</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
+        <is>
+          <t>5.2020-2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>CCE-CCE129</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>Ilson Wilmar Rodrigues Filho</t>
         </is>
@@ -686,45 +712,55 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>CIN7143</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>01342C</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Empreendedorismo I</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>1ª Fase</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>3.2020-2 / EF1-EFI402</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>3.2020-2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>EF1-EFI402</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>Sabrina Borges Ramos de Carvalho</t>
         </is>
@@ -733,45 +769,55 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>CIN7144</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>01342</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Tutoria Acadêmica I</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>1ª Fase</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2.1510-1 / CED-LBPREV</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
+        <is>
+          <t>2.1510-1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>CED-LBPREV</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>Ricardo Alexandre Reinaldo de Moraes</t>
         </is>
@@ -780,45 +826,55 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>CIN7145</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>01342</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Gestão da Informação</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>1ª Fase</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2.1620-2 / CED-103 C</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
+        <is>
+          <t>2.1620-2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>CED-103 C</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>Nathalia Berger Werlang</t>
         </is>
@@ -827,45 +883,55 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>CIN7201</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>02342A</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Sistemas de Organização do Conhecimento</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>2ª Fase</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>6.0820-4 / CED-004 D</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
+        <is>
+          <t>6.0820-4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>CED-004 D</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>Mariana Xavier de Oliveira</t>
         </is>
@@ -874,45 +940,55 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>CIN7201</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>02342C</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Sistemas de Organização do Conhecimento</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>2ª Fase</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>6.1830-4 / EF1-EFI405</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
+        <is>
+          <t>6.1830-4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>EF1-EFI405</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>Callu Ribeiro Ferreira Pedreira e Andrade Bamberg</t>
         </is>
@@ -921,45 +997,55 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>CIN7202</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>02342A</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Sociedade da Informação</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>2ª Fase</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>3.0820-2 / CED-LBTEC</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
+        <is>
+          <t>3.0820-2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>CED-LBTEC</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>Enrique Muriel Torrado</t>
         </is>
@@ -968,45 +1054,55 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>CIN7202</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>02342C</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Sociedade da Informação</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>2ª Fase</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>4.2020-2 / EF1-EFI305</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
+        <is>
+          <t>4.2020-2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>EF1-EFI305</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>Enrique Muriel Torrado</t>
         </is>
@@ -1015,45 +1111,55 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>CIN7203</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>02342A</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Ética Profissional</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>2ª Fase</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>5.0730-2 / CED-004 D</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
+        <is>
+          <t>5.0730-2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>CED-004 D</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>Callu Ribeiro Ferreira Pedreira e Andrade Bamberg</t>
         </is>
@@ -1062,45 +1168,55 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>CIN7203</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>02342C</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Ética Profissional</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>2ª Fase</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>4.1830-2 / EF1-EFI304</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
+        <is>
+          <t>4.1830-2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>EF1-EFI304</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>Callu Ribeiro Ferreira Pedreira e Andrade Bamberg</t>
         </is>
@@ -1109,45 +1225,55 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>CIN7204</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>02342C</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Tutoria Acadêmica II</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>2ª Fase</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>4.1710-1 / CED-105 B</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
+        <is>
+          <t>4.1710-1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>CED-105 B</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>Ricardo Alexandre Reinaldo de Moraes</t>
         </is>
@@ -1156,45 +1282,55 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>CIN7205</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>02342B</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Recuperação da Informação</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>2ª Fase</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2.1420-4 / CCE-516B</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
+        <is>
+          <t>2.1420-4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>CCE-516B</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>A contratar</t>
         </is>
@@ -1203,45 +1339,55 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>CIN7206</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>02342A</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Fontes Gerais de Informação</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>2ª Fase</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2.0820-2 / CED-102 C | 3.1010-2 / CED-102 C</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
+        <is>
+          <t>2.0820-2 | 3.1010-2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>CED-102 C | CED-102 C</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>Aline Carmes Krüger</t>
         </is>
@@ -1250,45 +1396,55 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>CIN7206</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>02342C</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Fontes Gerais de Informação</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>2ª Fase</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>3.1830-4 / CED-LBPREV</t>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
+        <is>
+          <t>3.1830-4</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>CED-LBPREV</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>Patricia da Silva Neubert</t>
         </is>
@@ -1297,45 +1453,55 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>CIN7301</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>03342A</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Introdução à Representação Temática</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>3ª Fase</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>3.0820-2 / CFH-1FH330</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
+        <is>
+          <t>3.0820-2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>CFH-1FH330</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>Mariana Xavier de Oliveira</t>
         </is>
@@ -1344,45 +1510,55 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>CIN7301</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>03342C</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Introdução à Representação Temática</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>3ª Fase</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>5.1830-2 / EF1-EFI304</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
+        <is>
+          <t>5.1830-2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>EF1-EFI304</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>Callu Ribeiro Ferreira Pedreira e Andrade Bamberg</t>
         </is>
@@ -1391,45 +1567,55 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>CIN7302</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>03342A</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Introdução à Representação Descritiva</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>3ª Fase</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>6.1010-2 / CED-LBPREV</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
+        <is>
+          <t>6.1010-2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>CED-LBPREV</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>Elizete Vieira Vitorino e Maria Zanela</t>
         </is>
@@ -1438,45 +1624,55 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>CIN7302</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>03342C</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Introdução à Representação Descritiva</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>3ª Fase</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>3.2020-2 / EF1-EFI401</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
+        <is>
+          <t>3.2020-2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>EF1-EFI401</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>Mariana Xavier de Oliveira</t>
         </is>
@@ -1485,45 +1681,55 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>CIN7303</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>03342A</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Metodologia da Pesquisa</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>3ª Fase</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>2.1010-2 / CED-LBPREV</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
+        <is>
+          <t>2.1010-2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>CED-LBPREV</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>Luis Roberto Sousa Mendes</t>
         </is>
@@ -1532,45 +1738,55 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>CIN7303</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>03342C</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Metodologia da Pesquisa</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>3ª Fase</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>2.2020-2 / CED-103 C</t>
-        </is>
-      </c>
       <c r="I21" t="inlineStr">
+        <is>
+          <t>2.2020-2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>CED-103 C</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>Maria Zanela e Elizete Vieira Vitorino</t>
         </is>
@@ -1579,45 +1795,55 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>CIN7304</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>03342A</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Introdução à Bancos de Dados</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>3ª Fase</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>4.0820-2 / CED-LBPREV</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
+        <is>
+          <t>4.0820-2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>CED-LBPREV</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>Gustavo Medeiros de Araújo</t>
         </is>
@@ -1626,45 +1852,55 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>CIN7304</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>03342C</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Introdução à Bancos de Dados</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>3ª Fase</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>5.2020-2 / CED-102 C</t>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
+        <is>
+          <t>5.2020-2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>CED-102 C</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>Gustavo Medeiros de Araújo</t>
         </is>
@@ -1673,45 +1909,55 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>CIN7306</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>03342A</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Competência Informacional</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>3ª Fase</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>6.0820-2 / CED-LBPREV</t>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
+        <is>
+          <t>6.0820-2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>CED-LBPREV</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>Maria Zanela e Elizete Vieira Vitorino</t>
         </is>
@@ -1720,45 +1966,55 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>CIN7306</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>03342C</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Competência Informacional</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>3ª Fase</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>2.1830-2 / CED-103 C</t>
-        </is>
-      </c>
       <c r="I25" t="inlineStr">
+        <is>
+          <t>2.1830-2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>CED-103 C</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>Maria Zanela e Elizete Vieira Vitorino</t>
         </is>
@@ -1767,45 +2023,55 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>CIN7309</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>03342A</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Gestão de Processos Organizacionais</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>3ª Fase</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>3.1010-2 / CED-LBTEC | 4.1010-2 / CED-LBTEC</t>
-        </is>
-      </c>
       <c r="I26" t="inlineStr">
+        <is>
+          <t>3.1010-2 | 4.1010-2</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>CED-LBTEC | CED-LBTEC</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>Rogerio da Silva Nunes</t>
         </is>
@@ -1814,45 +2080,55 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>CIN7309</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>03342C</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Gestão de Processos Organizacionais</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>3ª Fase</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>3.1830-2 / CED-LBTEC | 4.1830-2 / CED-LBTEC</t>
-        </is>
-      </c>
       <c r="I27" t="inlineStr">
+        <is>
+          <t>3.1830-2 | 4.1830-2</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>CED-LBTEC | CED-LBTEC</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>Rogerio da Silva Nunes</t>
         </is>
@@ -1861,45 +2137,55 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>CIN7401</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>04342A</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Estudos Métricos da Informação</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>4ª Fase</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>2.0820-4 / CED-103 C</t>
-        </is>
-      </c>
       <c r="I28" t="inlineStr">
+        <is>
+          <t>2.0820-4</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>CED-103 C</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>Adilson Luiz Pinto</t>
         </is>
@@ -1908,45 +2194,55 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>CIN7401</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>04342C</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Estudos Métricos da Informação</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>4ª Fase</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>3.1830-4 / CED-103 C</t>
-        </is>
-      </c>
       <c r="I29" t="inlineStr">
+        <is>
+          <t>3.1830-4</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>CED-103 C</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>Adilson Luiz Pinto</t>
         </is>
@@ -1955,45 +2251,55 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>CIN7402</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>04342A</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Editoração Científica</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>4ª Fase</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>6.1010-2 / CED-LBTEC</t>
-        </is>
-      </c>
       <c r="I30" t="inlineStr">
+        <is>
+          <t>6.1010-2</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>CED-LBTEC</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>Enrique Muriel Torrado</t>
         </is>
@@ -2002,45 +2308,55 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>CIN7402</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>04342C</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Editoração Científica</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>4ª Fase</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>6.1830-2 / CED-103 C</t>
-        </is>
-      </c>
       <c r="I31" t="inlineStr">
+        <is>
+          <t>6.1830-2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>CED-103 C</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>Enrique Muriel Torrado</t>
         </is>
@@ -2049,45 +2365,55 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>CIN7403</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>04342B</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Acessibilidade e Inclusão Digital</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>4ª Fase</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>4.1620-2 / CED-004 D</t>
-        </is>
-      </c>
       <c r="I32" t="inlineStr">
+        <is>
+          <t>4.1620-2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>CED-004 D</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>Ilson Wilmar Rodrigues Filho</t>
         </is>
@@ -2096,45 +2422,55 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>CIN7404</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>04342A</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Planejamento Estratégico</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>4ª Fase</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>4.0820-2 / CED-LBTEC</t>
-        </is>
-      </c>
       <c r="I33" t="inlineStr">
+        <is>
+          <t>4.0820-2</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>CED-LBTEC</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>Rogerio da Silva Nunes</t>
         </is>
@@ -2143,45 +2479,55 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>CIN7404</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>04342C</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Planejamento Estratégico</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>4ª Fase</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>6.2020-2 / CED-LBTEC</t>
-        </is>
-      </c>
       <c r="I34" t="inlineStr">
+        <is>
+          <t>6.2020-2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>CED-LBTEC</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>Sabrina Borges Ramos de Carvalho</t>
         </is>
@@ -2190,45 +2536,55 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>CIN7405</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>04342A</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>Projeto de Informatização</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>4ª Fase</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>5.1010-2 / CED-LBTEC</t>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
+        <is>
+          <t>5.1010-2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>CED-LBTEC</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
         <is>
           <t>Gustavo Medeiros de Araújo</t>
         </is>
@@ -2237,45 +2593,55 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>CIN7405</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>04342C</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>Projeto de Informatização</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>4ª Fase</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>4.2020-2 / CED-LBTEC</t>
-        </is>
-      </c>
       <c r="I36" t="inlineStr">
+        <is>
+          <t>4.2020-2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>CED-LBTEC</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
         <is>
           <t>Gustavo Medeiros de Araújo</t>
         </is>
@@ -2284,45 +2650,55 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>CIN7406</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>04342A</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>Preservação Digital</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>4ª Fase</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>6.0820-2 / CED-LBTEC</t>
-        </is>
-      </c>
       <c r="I37" t="inlineStr">
+        <is>
+          <t>6.0820-2</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>CED-LBTEC</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
         <is>
           <t>Camila Schwinden Lehmkuhl</t>
         </is>
@@ -2331,45 +2707,55 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>CIN7406</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>04342C</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Preservação Digital</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>4ª Fase</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>2.2020-2 / CED-LBPREV</t>
-        </is>
-      </c>
       <c r="I38" t="inlineStr">
+        <is>
+          <t>2.2020-2</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>CED-LBPREV</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
         <is>
           <t>Sabrina Borges Ramos de Carvalho</t>
         </is>
@@ -2378,45 +2764,55 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>CIN7412</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>04342A</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>Marketing da Informação</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>4ª Fase</t>
-        </is>
-      </c>
       <c r="E39" t="inlineStr">
         <is>
+          <t>2ª Fase</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>3.1010-2 / CED-004 D</t>
-        </is>
-      </c>
       <c r="I39" t="inlineStr">
+        <is>
+          <t>3.1010-2</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>CED-004 D</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
         <is>
           <t>Sonali Paula Molin Bedin</t>
         </is>
@@ -2425,45 +2821,55 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>CIN7412</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>04342C</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>Marketing da Informação</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>4ª Fase</t>
-        </is>
-      </c>
       <c r="E40" t="inlineStr">
         <is>
+          <t>2ª Fase</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>5.2020-2 / EF1-EFI301</t>
-        </is>
-      </c>
       <c r="I40" t="inlineStr">
+        <is>
+          <t>5.2020-2</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>EF1-EFI301</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
         <is>
           <t>Sabrina Borges Ramos de Carvalho</t>
         </is>
@@ -2472,45 +2878,55 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>CIN7501</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>05342</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>Arquitetura da Informação e Usabilidade</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>5ª Fase</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>2.2020-2 / CCE-516B</t>
-        </is>
-      </c>
       <c r="I41" t="inlineStr">
+        <is>
+          <t>2.2020-2</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>CCE-516B</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
         <is>
           <t>Márcio Matias</t>
         </is>
@@ -2519,45 +2935,55 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>CIN7502</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>05342</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>Mineração de Texto</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>5ª Fase</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>3.2020-2 / CCE-CCE129</t>
-        </is>
-      </c>
       <c r="I42" t="inlineStr">
+        <is>
+          <t>3.2020-2</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>CCE-CCE129</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>Flavio Augusto Carraro</t>
         </is>
@@ -2566,45 +2992,55 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>CIN7503</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>05342</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>Bancos de Dados</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>5ª Fase</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>6.2020-2 / CCE-CCE131</t>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
+        <is>
+          <t>6.2020-2</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>CCE-CCE131</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
         <is>
           <t>Flavio Augusto Carraro</t>
         </is>
@@ -2613,45 +3049,55 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>CIN7504</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>05342</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>Gerenciamento de Projetos</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>5ª Fase</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>6.1830-2 / CCE-CCE129</t>
-        </is>
-      </c>
       <c r="I44" t="inlineStr">
+        <is>
+          <t>6.1830-2</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>CCE-CCE129</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
         <is>
           <t>Sabrina Borges Ramos de Carvalho</t>
         </is>
@@ -2660,45 +3106,55 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
           <t>CIN7505</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>05342</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>Estágio em Ciência da Informação</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>5ª Fase</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>432</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>2.1420-2 / CED-105 B</t>
-        </is>
-      </c>
       <c r="I45" t="inlineStr">
+        <is>
+          <t>2.1420-2</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>CED-105 B</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
         <is>
           <t>Nathalia Berger Werlang</t>
         </is>
@@ -2707,45 +3163,55 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>CIN7601</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>06342</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>Linked Data</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>6ª Fase</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>3.1830-2 / CCE-CCE131</t>
-        </is>
-      </c>
       <c r="I46" t="inlineStr">
+        <is>
+          <t>3.1830-2</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>CCE-CCE131</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
         <is>
           <t>Flavio Augusto Carraro</t>
         </is>
@@ -2754,45 +3220,55 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>CIN7602</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>06342</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>Mídias Sociais</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>6ª Fase</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>6.1830-2 / CCE-CCE131</t>
-        </is>
-      </c>
       <c r="I47" t="inlineStr">
+        <is>
+          <t>6.1830-2</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>CCE-CCE131</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
         <is>
           <t>Flavio Augusto Carraro</t>
         </is>
@@ -2801,45 +3277,55 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>CIN7603</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>06342</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>Empreendedorismo II</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>6ª Fase</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>2.1830-4 / CCE-CCE129</t>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
+        <is>
+          <t>2.1830-4</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>CCE-CCE129</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
         <is>
           <t>Nathalia Berger Werlang</t>
         </is>
@@ -2848,45 +3334,55 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>CIN7604</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>06342</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>TCC</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>6ª Fase</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>4.1620-2 / EF1-EFI303</t>
-        </is>
-      </c>
       <c r="I49" t="inlineStr">
+        <is>
+          <t>4.1620-2</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>EF1-EFI303</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
         <is>
           <t>Márcio Matias</t>
         </is>
@@ -2895,45 +3391,55 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>CIN7904</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>05342</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>Avaliação de Desempenho</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Optativa</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Optativa</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>4.1830-2 / CCE-CCE129</t>
-        </is>
-      </c>
       <c r="I50" t="inlineStr">
+        <is>
+          <t>4.1830-2</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>CCE-CCE129</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
         <is>
           <t>A contratar</t>
         </is>
@@ -2942,45 +3448,55 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>CIN7906</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>05342</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>Inovação e Informação</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>Optativa</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Optativa</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>3.1830-2 / CCE-CCE129 | 5.1830-2 / CCE-CCE129</t>
-        </is>
-      </c>
       <c r="I51" t="inlineStr">
+        <is>
+          <t>3.1830-2 | 5.1830-2</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>CCE-CCE129 | CCE-CCE129</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
         <is>
           <t>Sabrina Borges Ramos de Carvalho</t>
         </is>
@@ -2989,45 +3505,55 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>CIN7907</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>02342</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Lógica Aplicada I</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>2ª Fase</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>5.1830-4 / CCE-CCE131</t>
-        </is>
-      </c>
       <c r="I52" t="inlineStr">
+        <is>
+          <t>5.1830-4</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>CCE-CCE131</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
         <is>
           <t>Ricardo Alexandre Reinaldo de Moraes e Flavio Augusto Carraro</t>
         </is>
@@ -3036,45 +3562,55 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>CIN7913</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>04342</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>Lógica Instrumental II</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>Optativa</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>Optativa</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>4.1420-2 / CED-LBPREV</t>
-        </is>
-      </c>
       <c r="I53" t="inlineStr">
+        <is>
+          <t>4.1420-2</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>CED-LBPREV</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
         <is>
           <t>Ilson Wilmar Rodrigues Filho</t>
         </is>
@@ -3083,45 +3619,55 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>CIN7917</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>06342</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>Visualização da Informação</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>Optativa</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>Optativa</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>4.1830-2 / CCE-516B</t>
-        </is>
-      </c>
       <c r="I54" t="inlineStr">
+        <is>
+          <t>4.1830-2</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>CCE-516B</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
         <is>
           <t>Márcio Matias</t>
         </is>
@@ -3130,45 +3676,55 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>CIN7919</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>05342</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>Informação, Direito e Cidadania</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Optativa</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Optativa</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>4.2020-2 / CCE-516B</t>
-        </is>
-      </c>
       <c r="I55" t="inlineStr">
+        <is>
+          <t>4.2020-2</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>CCE-516B</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
         <is>
           <t>Luis Roberto Sousa Mendes</t>
         </is>
@@ -3177,45 +3733,55 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
           <t>CIN7925</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>01342</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>Introdução a Algoritmos</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>1ª Fase</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>4.1830-2 / CCE-CCE131</t>
-        </is>
-      </c>
       <c r="I56" t="inlineStr">
+        <is>
+          <t>4.1830-2</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>CCE-CCE131</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
         <is>
           <t>Flavio Augusto Carraro</t>
         </is>
@@ -3224,45 +3790,55 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
           <t>CIN7935</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>06342</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>Liderança e Gerência</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>Optativa</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>Optativa</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>2.1830-2 / CCE-CCE131</t>
-        </is>
-      </c>
       <c r="I57" t="inlineStr">
+        <is>
+          <t>2.1830-2</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>CCE-CCE131</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
         <is>
           <t>Sabrina Borges Ramos de Carvalho</t>
         </is>
@@ -3271,45 +3847,55 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
           <t>CIN7936</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>03342A</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>Proteção de Dados Pessoais</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>3ª Fase</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>2.0820-2 / CED-LBPREV</t>
-        </is>
-      </c>
       <c r="I58" t="inlineStr">
+        <is>
+          <t>2.0820-2</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>CED-LBPREV</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
         <is>
           <t>Marcelo Minghelli</t>
         </is>
@@ -3318,45 +3904,55 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
           <t>CIN7936</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>03342C</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>Proteção de Dados Pessoais</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>3ª Fase</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>4.2020-2 / CED-102 C</t>
-        </is>
-      </c>
       <c r="I59" t="inlineStr">
+        <is>
+          <t>4.2020-2</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>CED-102 C</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
         <is>
           <t>Marcelo Minghelli</t>
         </is>
@@ -3365,45 +3961,55 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
           <t>CIN7943</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>01342</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>Experiência do Usuário (UX) User Experience</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>1ª Fase</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>4.2020-2 / CCE-CCE131</t>
-        </is>
-      </c>
       <c r="I60" t="inlineStr">
+        <is>
+          <t>4.2020-2</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>CCE-CCE131</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
         <is>
           <t>Márcio Matias</t>
         </is>
@@ -3412,45 +4018,55 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
           <t>CIN7944</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>06342</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>Curadoria Digital</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>Optativa</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Optativa</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>4.2020-2 / CCE-CCE129</t>
-        </is>
-      </c>
       <c r="I61" t="inlineStr">
+        <is>
+          <t>4.2020-2</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>CCE-CCE129</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
         <is>
           <t>Flavio Augusto Carraro</t>
         </is>
@@ -3459,45 +4075,55 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
           <t>CIN7945</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>05342</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>Fontes de Informação Tecnológica</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>Optativa</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>Optativa</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>2.1830-2 / CCE-516B</t>
-        </is>
-      </c>
       <c r="I62" t="inlineStr">
+        <is>
+          <t>2.1830-2</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>CCE-516B</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
         <is>
           <t>Márcio Matias</t>
         </is>
@@ -3506,45 +4132,55 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
           <t>CIN7950</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>06342</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>Programa de Intercâmbio I</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>Optativa</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>Optativa</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>A definir</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>A definir</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
         <is>
           <t>A contratar</t>
         </is>
@@ -3553,45 +4189,55 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
           <t>HST7921</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>03342A</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>História do Brasil Contemporâneo</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>3ª Fase</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>5.0820-4 / CED-LBPREV</t>
-        </is>
-      </c>
       <c r="I64" t="inlineStr">
+        <is>
+          <t>5.0820-4</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>CED-LBPREV</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
         <is>
           <t>Roselane Neckel</t>
         </is>
@@ -3600,45 +4246,55 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
           <t>HST7921</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>03342C</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>História do Brasil Contemporâneo</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>3ª Fase</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>6.1830-4 / CFH-1FH322</t>
-        </is>
-      </c>
       <c r="I65" t="inlineStr">
+        <is>
+          <t>6.1830-4</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>CFH-1FH322</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
         <is>
           <t>Roselane Neckel</t>
         </is>
@@ -3647,45 +4303,55 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
           <t>INE5111</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>04342A</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>Estatística Aplicada I</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>2ª Fase</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>3.0820-2 / CED-LBPREV | 4.1010-2 / CED-LBPREV</t>
-        </is>
-      </c>
       <c r="I66" t="inlineStr">
+        <is>
+          <t>3.0820-2 | 4.1010-2</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>CED-LBPREV | CED-LBPREV</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
         <is>
           <t>Vera do Carmo Comparsi de Vargas</t>
         </is>
@@ -3694,45 +4360,55 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
           <t>INE5111</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>04342C</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>Estatística Aplicada I</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>2ª Fase</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>2.1830-2 / CTC-CTC106 | 5.1830-2 / CTC-CTC106</t>
-        </is>
-      </c>
       <c r="I67" t="inlineStr">
+        <is>
+          <t>2.1830-2 | 5.1830-2</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>CTC-CTC106 | CTC-CTC106</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
         <is>
           <t>Manoella Reis Cardenuto</t>
         </is>
@@ -3741,45 +4417,55 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
           <t>LLV7802</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>01342C</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>Leitura e Produção do Texto</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>1ª Fase</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>6.1830-4 / EF1-EFI304</t>
-        </is>
-      </c>
       <c r="I68" t="inlineStr">
+        <is>
+          <t>6.1830-4</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>EF1-EFI304</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
         <is>
           <t>Graziela Hahn</t>
         </is>
@@ -3788,45 +4474,55 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
           <t>LLV7802</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>01342D</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>Leitura e Produção do Texto</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>1ª Fase</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>6.1830-4 / EF1-EFI304</t>
-        </is>
-      </c>
       <c r="I69" t="inlineStr">
+        <is>
+          <t>6.1830-4</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>EF1-EFI304</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
         <is>
           <t>Graziela Hahn</t>
         </is>
@@ -3835,45 +4531,55 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
           <t>MTM3110</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>01342</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>Cálculo</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>1ª Fase</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>3.1830-2 / EF1-EFI405 | 5.1830-2 / EF1-EFI405</t>
-        </is>
-      </c>
       <c r="I70" t="inlineStr">
+        <is>
+          <t>3.1830-2 | 5.1830-2</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>EF1-EFI405 | EF1-EFI405</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
         <is>
           <t>Camilo Campana e Camila Aparecida Benedito Rodrigues de Lima</t>
         </is>
@@ -3895,8 +4601,8 @@
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="63" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="63" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="38" customWidth="1" min="6" max="6"/>
   </cols>
@@ -4403,6 +5109,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>Professor</t>
         </is>
       </c>
@@ -4420,6 +5131,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>CCE-CCE129</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>Ilson Wilmar Rodrigues Filho</t>
         </is>
       </c>
@@ -4437,6 +5153,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>EF1-EFI402</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>Sabrina Borges Ramos de Carvalho</t>
         </is>
       </c>
@@ -4454,6 +5175,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>CED-LBPREV</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>Ricardo Alexandre Reinaldo de Moraes</t>
         </is>
       </c>
@@ -4471,6 +5197,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>CED-103 C</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>Nathalia Berger Werlang</t>
         </is>
       </c>
@@ -4488,6 +5219,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>CCE-CCE131</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>Flavio Augusto Carraro</t>
         </is>
       </c>
@@ -4505,6 +5241,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>CCE-CCE131</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>Márcio Matias</t>
         </is>
       </c>
@@ -4522,6 +5263,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>EF1-EFI304</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>Graziela Hahn</t>
         </is>
       </c>
@@ -4539,6 +5285,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>EF1-EFI304</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>Graziela Hahn</t>
         </is>
       </c>
@@ -4555,6 +5306,11 @@
         </is>
       </c>
       <c r="C28" t="inlineStr">
+        <is>
+          <t>EF1-EFI405 | EF1-EFI405</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>Camilo Campana e Camila Aparecida Benedito Rodrigues de Lima</t>
         </is>
@@ -4575,13 +5331,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="64" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="64" customWidth="1" min="4" max="4"/>
     <col width="37" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
@@ -4727,7 +5483,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CIN7206 (02342A)</t>
+          <t>CIN7206 (02342A) / CIN7412 (04342A)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4759,7 +5515,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CIN7206 (02342A)</t>
+          <t>CIN7206 (02342A) / CIN7412 (04342A)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -5025,7 +5781,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CIN7907 (02342)</t>
+          <t>CIN7412 (04342C) / CIN7907 (02342)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -5057,7 +5813,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CIN7907 (02342)</t>
+          <t>CIN7412 (04342C) / CIN7907 (02342)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -5088,6 +5844,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>Professor</t>
         </is>
       </c>
@@ -5105,6 +5866,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>CED-004 D</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>Mariana Xavier de Oliveira</t>
         </is>
       </c>
@@ -5122,6 +5888,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>EF1-EFI405</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>Callu Ribeiro Ferreira Pedreira e Andrade Bamberg</t>
         </is>
       </c>
@@ -5139,6 +5910,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>CED-LBTEC</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>Enrique Muriel Torrado</t>
         </is>
       </c>
@@ -5156,6 +5932,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>EF1-EFI305</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>Enrique Muriel Torrado</t>
         </is>
       </c>
@@ -5173,6 +5954,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>CED-004 D</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>Callu Ribeiro Ferreira Pedreira e Andrade Bamberg</t>
         </is>
       </c>
@@ -5190,6 +5976,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>EF1-EFI304</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>Callu Ribeiro Ferreira Pedreira e Andrade Bamberg</t>
         </is>
       </c>
@@ -5207,6 +5998,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>CED-105 B</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>Ricardo Alexandre Reinaldo de Moraes</t>
         </is>
       </c>
@@ -5224,6 +6020,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>CCE-516B</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>?</t>
         </is>
       </c>
@@ -5241,6 +6042,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>CED-102 C | CED-102 C</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>Aline Carmes Krüger</t>
         </is>
       </c>
@@ -5258,6 +6064,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>CED-LBPREV</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
           <t>Patricia da Silva Neubert</t>
         </is>
       </c>
@@ -5265,49 +6076,108 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CIN7907 (02342)</t>
+          <t>CIN7412 (04342A)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Lógica Aplicada I</t>
+          <t>Marketing da Informação</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ricardo Alexandre Reinaldo de Moraes e Flavio Augusto Carraro</t>
+          <t>CED-004 D</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Sonali Paula Molin Bedin</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>INE5111 (04342A)</t>
+          <t>CIN7412 (04342C)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Estatística Aplicada I</t>
+          <t>Marketing da Informação</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Vera do Carmo Comparsi de Vargas</t>
+          <t>EF1-EFI301</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Sabrina Borges Ramos de Carvalho</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>CIN7907 (02342)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Lógica Aplicada I</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CCE-CCE131</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Ricardo Alexandre Reinaldo de Moraes e Flavio Augusto Carraro</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>INE5111 (04342A)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Estatística Aplicada I</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CED-LBPREV | CED-LBPREV</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Vera do Carmo Comparsi de Vargas</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>INE5111 (04342C)</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Estatística Aplicada I</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CTC-CTC106 | CTC-CTC106</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>Manoella Reis Cardenuto</t>
         </is>
@@ -5333,8 +6203,8 @@
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
@@ -5841,6 +6711,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>Professor</t>
         </is>
       </c>
@@ -5858,6 +6733,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>CFH-1FH330</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>Mariana Xavier de Oliveira</t>
         </is>
       </c>
@@ -5875,6 +6755,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>EF1-EFI304</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>Callu Ribeiro Ferreira Pedreira e Andrade Bamberg</t>
         </is>
       </c>
@@ -5892,6 +6777,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>CED-LBPREV</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>Elizete Vieira Vitorino e Maria Zanela</t>
         </is>
       </c>
@@ -5909,6 +6799,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>EF1-EFI401</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>Mariana Xavier de Oliveira</t>
         </is>
       </c>
@@ -5926,6 +6821,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>CED-LBPREV</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>Luis Roberto Sousa Mendes</t>
         </is>
       </c>
@@ -5943,6 +6843,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>CED-103 C</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>Maria Zanela e Elizete Vieira Vitorino</t>
         </is>
       </c>
@@ -5960,6 +6865,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>CED-LBPREV</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>Gustavo Medeiros de Araújo</t>
         </is>
       </c>
@@ -5977,6 +6887,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>CED-102 C</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>Gustavo Medeiros de Araújo</t>
         </is>
       </c>
@@ -5994,6 +6909,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>CED-LBPREV</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>Maria Zanela e Elizete Vieira Vitorino</t>
         </is>
       </c>
@@ -6011,6 +6931,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>CED-103 C</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
           <t>Maria Zanela e Elizete Vieira Vitorino</t>
         </is>
       </c>
@@ -6028,6 +6953,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>CED-LBTEC | CED-LBTEC</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
           <t>Rogerio da Silva Nunes</t>
         </is>
       </c>
@@ -6045,6 +6975,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>CED-LBTEC | CED-LBTEC</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t>Rogerio da Silva Nunes</t>
         </is>
       </c>
@@ -6062,6 +6997,11 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>CED-LBPREV</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
           <t>Marcelo Minghelli</t>
         </is>
       </c>
@@ -6079,6 +7019,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>CED-102 C</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>Marcelo Minghelli</t>
         </is>
       </c>
@@ -6096,6 +7041,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>CED-LBPREV</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
           <t>Roselane Neckel</t>
         </is>
       </c>
@@ -6112,6 +7062,11 @@
         </is>
       </c>
       <c r="C35" t="inlineStr">
+        <is>
+          <t>CFH-1FH322</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>Roselane Neckel</t>
         </is>
@@ -6132,13 +7087,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
@@ -6284,7 +7239,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CIN7412 (04342A)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -6316,7 +7271,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CIN7412 (04342A)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -6582,7 +7537,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CIN7412 (04342C)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -6614,7 +7569,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CIN7412 (04342C)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -6645,6 +7600,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>Professor</t>
         </is>
       </c>
@@ -6662,6 +7622,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>CED-103 C</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>Adilson Luiz Pinto</t>
         </is>
       </c>
@@ -6679,6 +7644,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>CED-103 C</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>Adilson Luiz Pinto</t>
         </is>
       </c>
@@ -6696,6 +7666,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>CED-LBTEC</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>Enrique Muriel Torrado</t>
         </is>
       </c>
@@ -6713,6 +7688,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>CED-103 C</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>Enrique Muriel Torrado</t>
         </is>
       </c>
@@ -6730,6 +7710,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>CED-004 D</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>Ilson Wilmar Rodrigues Filho</t>
         </is>
       </c>
@@ -6747,6 +7732,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>CED-LBTEC</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>Rogerio da Silva Nunes</t>
         </is>
       </c>
@@ -6764,6 +7754,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>CED-LBTEC</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>Sabrina Borges Ramos de Carvalho</t>
         </is>
       </c>
@@ -6781,6 +7776,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>CED-LBTEC</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>Gustavo Medeiros de Araújo</t>
         </is>
       </c>
@@ -6798,6 +7798,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>CED-LBTEC</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>Gustavo Medeiros de Araújo</t>
         </is>
       </c>
@@ -6815,6 +7820,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>CED-LBTEC</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
           <t>Camila Schwinden Lehmkuhl</t>
         </is>
       </c>
@@ -6832,39 +7842,10 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sabrina Borges Ramos de Carvalho</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>CIN7412 (04342A)</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Marketing da Informação</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Sonali Paula Molin Bedin</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>CIN7412 (04342C)</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Marketing da Informação</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
+          <t>CED-LBPREV</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>Sabrina Borges Ramos de Carvalho</t>
         </is>
@@ -6890,8 +7871,8 @@
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
@@ -7398,6 +8379,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>Professor</t>
         </is>
       </c>
@@ -7415,6 +8401,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>CCE-516B</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>Márcio Matias</t>
         </is>
       </c>
@@ -7432,6 +8423,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>CCE-CCE129</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>Flavio Augusto Carraro</t>
         </is>
       </c>
@@ -7449,6 +8445,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>CCE-CCE131</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>Flavio Augusto Carraro</t>
         </is>
       </c>
@@ -7466,6 +8467,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>CCE-CCE129</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>Sabrina Borges Ramos de Carvalho</t>
         </is>
       </c>
@@ -7482,6 +8488,11 @@
         </is>
       </c>
       <c r="C24" t="inlineStr">
+        <is>
+          <t>CED-105 B</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>Nathalia Berger Werlang</t>
         </is>
@@ -7507,8 +8518,8 @@
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
@@ -8015,6 +9026,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>Professor</t>
         </is>
       </c>
@@ -8032,6 +9048,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>CCE-CCE131</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>Flavio Augusto Carraro</t>
         </is>
       </c>
@@ -8049,6 +9070,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>CCE-CCE131</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>Flavio Augusto Carraro</t>
         </is>
       </c>
@@ -8066,6 +9092,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>CCE-CCE129</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>Nathalia Berger Werlang</t>
         </is>
       </c>
@@ -8082,6 +9113,11 @@
         </is>
       </c>
       <c r="C23" t="inlineStr">
+        <is>
+          <t>EF1-EFI303</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>Márcio Matias</t>
         </is>
